--- a/output/topology_excel/9825.xlsx
+++ b/output/topology_excel/9825.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F61"/>
+  <dimension ref="A1:H61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,22 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Length</t>
+          <t>Length_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Width</t>
+          <t>Width_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Length_2</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Width_2</t>
         </is>
       </c>
     </row>
@@ -481,6 +491,8 @@
       <c r="F2" t="n">
         <v>13</v>
       </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -503,6 +515,8 @@
       <c r="F3" t="n">
         <v>13</v>
       </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -525,6 +539,8 @@
       <c r="F4" t="n">
         <v>69</v>
       </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -547,6 +563,8 @@
       <c r="F5" t="n">
         <v>65</v>
       </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -569,6 +587,8 @@
       <c r="F6" t="n">
         <v>13</v>
       </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -591,6 +611,8 @@
       <c r="F7" t="n">
         <v>13</v>
       </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -613,6 +635,8 @@
       <c r="F8" t="n">
         <v>13</v>
       </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -635,6 +659,8 @@
       <c r="F9" t="n">
         <v>13</v>
       </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -657,6 +683,8 @@
       <c r="F10" t="n">
         <v>13</v>
       </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -679,6 +707,8 @@
       <c r="F11" t="n">
         <v>13</v>
       </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -701,6 +731,8 @@
       <c r="F12" t="n">
         <v>13</v>
       </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -723,6 +755,8 @@
       <c r="F13" t="n">
         <v>13</v>
       </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -745,6 +779,8 @@
       <c r="F14" t="n">
         <v>13</v>
       </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -767,6 +803,8 @@
       <c r="F15" t="n">
         <v>13</v>
       </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -789,6 +827,8 @@
       <c r="F16" t="n">
         <v>13</v>
       </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -811,6 +851,8 @@
       <c r="F17" t="n">
         <v>13</v>
       </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -833,6 +875,8 @@
       <c r="F18" t="n">
         <v>13</v>
       </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -855,6 +899,8 @@
       <c r="F19" t="n">
         <v>13</v>
       </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -877,6 +923,8 @@
       <c r="F20" t="n">
         <v>13</v>
       </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -891,13 +939,19 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>219</v>
+        <v>206</v>
       </c>
       <c r="F21" t="n">
-        <v>65</v>
+        <v>13</v>
+      </c>
+      <c r="G21" t="n">
+        <v>52</v>
+      </c>
+      <c r="H21" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="22">
@@ -921,6 +975,8 @@
       <c r="F22" t="n">
         <v>13</v>
       </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -943,6 +999,8 @@
       <c r="F23" t="n">
         <v>23</v>
       </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -965,6 +1023,8 @@
       <c r="F24" t="n">
         <v>13</v>
       </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -987,6 +1047,8 @@
       <c r="F25" t="n">
         <v>13</v>
       </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1001,13 +1063,19 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E26" t="n">
-        <v>201</v>
+        <v>188</v>
       </c>
       <c r="F26" t="n">
-        <v>141</v>
+        <v>13</v>
+      </c>
+      <c r="G26" t="n">
+        <v>128</v>
+      </c>
+      <c r="H26" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="27">
@@ -1031,6 +1099,8 @@
       <c r="F27" t="n">
         <v>13</v>
       </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1053,6 +1123,8 @@
       <c r="F28" t="n">
         <v>13</v>
       </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1075,6 +1147,8 @@
       <c r="F29" t="n">
         <v>13</v>
       </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1097,6 +1171,8 @@
       <c r="F30" t="n">
         <v>13</v>
       </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1119,6 +1195,8 @@
       <c r="F31" t="n">
         <v>13</v>
       </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1141,6 +1219,8 @@
       <c r="F32" t="n">
         <v>13</v>
       </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1163,6 +1243,8 @@
       <c r="F33" t="n">
         <v>13</v>
       </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1177,13 +1259,19 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E34" t="n">
-        <v>198</v>
+        <v>185</v>
       </c>
       <c r="F34" t="n">
-        <v>141</v>
+        <v>13</v>
+      </c>
+      <c r="G34" t="n">
+        <v>128</v>
+      </c>
+      <c r="H34" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="35">
@@ -1207,6 +1295,8 @@
       <c r="F35" t="n">
         <v>13</v>
       </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1229,6 +1319,8 @@
       <c r="F36" t="n">
         <v>13</v>
       </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1243,13 +1335,19 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E37" t="n">
-        <v>214</v>
+        <v>201</v>
       </c>
       <c r="F37" t="n">
-        <v>60</v>
+        <v>13</v>
+      </c>
+      <c r="G37" t="n">
+        <v>47</v>
+      </c>
+      <c r="H37" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="38">
@@ -1273,6 +1371,8 @@
       <c r="F38" t="n">
         <v>13</v>
       </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1293,8 +1393,10 @@
         <v>136</v>
       </c>
       <c r="F39" t="n">
-        <v>84</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1317,6 +1419,8 @@
       <c r="F40" t="n">
         <v>13</v>
       </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1337,8 +1441,10 @@
         <v>142</v>
       </c>
       <c r="F41" t="n">
-        <v>86</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1361,6 +1467,8 @@
       <c r="F42" t="n">
         <v>13</v>
       </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1383,6 +1491,8 @@
       <c r="F43" t="n">
         <v>13</v>
       </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1405,6 +1515,8 @@
       <c r="F44" t="n">
         <v>13</v>
       </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1427,6 +1539,8 @@
       <c r="F45" t="n">
         <v>13</v>
       </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -1449,6 +1563,8 @@
       <c r="F46" t="n">
         <v>13</v>
       </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1471,6 +1587,8 @@
       <c r="F47" t="n">
         <v>13</v>
       </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -1493,6 +1611,8 @@
       <c r="F48" t="n">
         <v>13</v>
       </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -1515,6 +1635,8 @@
       <c r="F49" t="n">
         <v>13</v>
       </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -1537,6 +1659,8 @@
       <c r="F50" t="n">
         <v>13</v>
       </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -1559,6 +1683,8 @@
       <c r="F51" t="n">
         <v>13</v>
       </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -1581,6 +1707,8 @@
       <c r="F52" t="n">
         <v>13</v>
       </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -1603,6 +1731,8 @@
       <c r="F53" t="n">
         <v>23</v>
       </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -1625,6 +1755,8 @@
       <c r="F54" t="n">
         <v>13</v>
       </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -1647,6 +1779,8 @@
       <c r="F55" t="n">
         <v>13</v>
       </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -1669,6 +1803,8 @@
       <c r="F56" t="n">
         <v>13</v>
       </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -1691,6 +1827,8 @@
       <c r="F57" t="n">
         <v>13</v>
       </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -1713,6 +1851,8 @@
       <c r="F58" t="n">
         <v>23</v>
       </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -1735,6 +1875,8 @@
       <c r="F59" t="n">
         <v>35</v>
       </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -1757,6 +1899,8 @@
       <c r="F60" t="n">
         <v>35</v>
       </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -1779,6 +1923,8 @@
       <c r="F61" t="n">
         <v>23</v>
       </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
